--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="45" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{379357EB-1451-4751-B68C-EC4509A7C402}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E06A2C56-302A-46DC-968A-FCD764C654B4}"/>
   <bookViews>
-    <workbookView xWindow="2595" yWindow="885" windowWidth="21600" windowHeight="11385" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ON" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>Sets the maximum capacity of technologies by period.</t>
   </si>
@@ -109,6 +109,15 @@
   </si>
   <si>
     <t>E_HYD_DLY-NEW</t>
+  </si>
+  <si>
+    <t>reference</t>
+  </si>
+  <si>
+    <t>biogas potential</t>
+  </si>
+  <si>
+    <t>hydro potential</t>
   </si>
 </sst>
 </file>
@@ -150,8 +159,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -466,23 +476,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D36A0F-FD90-42AA-87C7-33795DBA1E16}">
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:H25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1</v>
       </c>
@@ -504,8 +514,11 @@
       <c r="G3">
         <v>2050</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
@@ -527,8 +540,9 @@
       <c r="G4">
         <v>1000</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="1"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>14</v>
       </c>
@@ -551,7 +565,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -574,7 +588,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>16</v>
       </c>
@@ -597,7 +611,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
@@ -620,7 +634,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -643,7 +657,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>19</v>
       </c>
@@ -666,7 +680,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -689,7 +703,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>21</v>
       </c>
@@ -712,7 +726,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>22</v>
       </c>
@@ -735,7 +749,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>3</v>
       </c>
@@ -758,7 +772,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>4</v>
       </c>
@@ -781,7 +795,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>5</v>
       </c>
@@ -804,7 +818,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
@@ -827,7 +841,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>7</v>
       </c>
@@ -850,7 +864,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>8</v>
       </c>
@@ -873,7 +887,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>9</v>
       </c>
@@ -896,7 +910,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -919,7 +933,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>11</v>
       </c>
@@ -942,7 +956,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -965,7 +979,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -987,8 +1001,11 @@
       <c r="G24">
         <v>320</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>24</v>
       </c>
@@ -1009,6 +1026,9 @@
       </c>
       <c r="G25">
         <v>4000</v>
+      </c>
+      <c r="H25" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="128" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA1DC616-41B6-4427-8CE5-7E878A34A2B5}"/>
+  <xr:revisionPtr revIDLastSave="139" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08131A89-F3AB-48F6-BB95-5DB5CDCD5232}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="47">
   <si>
     <t>tech</t>
   </si>
@@ -135,9 +135,6 @@
     <t>New biogas generation potential for ontario</t>
   </si>
   <si>
-    <t>New hydroelectric generation potential for ontario. Half assumed to be run-of-river, the other half daily storage.</t>
-  </si>
-  <si>
     <t>Assumed that Ontario does not have requisite geology for geothermal generation</t>
   </si>
   <si>
@@ -166,6 +163,18 @@
   </si>
   <si>
     <t>E_HYD_ROR-NEW-5</t>
+  </si>
+  <si>
+    <t>New hydroelectric generation potential for ontario. Half assumed to be run-of-river, the other half daily storage (similar to existing).</t>
+  </si>
+  <si>
+    <t>E_COAL-NEW</t>
+  </si>
+  <si>
+    <t>E_COAL_CCS-NEW</t>
+  </si>
+  <si>
+    <t>Assume no new coal generation</t>
   </si>
 </sst>
 </file>
@@ -524,7 +533,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D36A0F-FD90-42AA-87C7-33795DBA1E16}">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -1168,7 +1177,7 @@
         <v>2500</v>
       </c>
       <c r="H25" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -1179,7 +1188,7 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -1200,12 +1209,12 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -1226,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I27">
         <v>1</v>
@@ -1237,7 +1246,7 @@
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -1258,7 +1267,7 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="I28">
         <v>1</v>
@@ -1269,7 +1278,7 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29">
         <v>500</v>
@@ -1290,7 +1299,7 @@
         <v>500</v>
       </c>
       <c r="H29" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I29">
         <v>2</v>
@@ -1301,7 +1310,7 @@
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30">
         <v>500</v>
@@ -1322,7 +1331,7 @@
         <v>500</v>
       </c>
       <c r="H30" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I30">
         <v>2</v>
@@ -1333,7 +1342,7 @@
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31">
         <v>500</v>
@@ -1354,7 +1363,7 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I31">
         <v>2</v>
@@ -1365,7 +1374,7 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B32">
         <v>500</v>
@@ -1386,7 +1395,7 @@
         <v>500</v>
       </c>
       <c r="H32" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="I32">
         <v>2</v>
@@ -1397,34 +1406,86 @@
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33">
+        <v>500</v>
+      </c>
+      <c r="C33">
+        <v>500</v>
+      </c>
+      <c r="D33">
+        <v>500</v>
+      </c>
+      <c r="E33">
+        <v>500</v>
+      </c>
+      <c r="F33">
+        <v>500</v>
+      </c>
+      <c r="G33">
+        <v>500</v>
+      </c>
+      <c r="H33" t="s">
         <v>43</v>
-      </c>
-      <c r="B33">
-        <v>500</v>
-      </c>
-      <c r="C33">
-        <v>500</v>
-      </c>
-      <c r="D33">
-        <v>500</v>
-      </c>
-      <c r="E33">
-        <v>500</v>
-      </c>
-      <c r="F33">
-        <v>500</v>
-      </c>
-      <c r="G33">
-        <v>500</v>
-      </c>
-      <c r="H33" t="s">
-        <v>33</v>
       </c>
       <c r="I33">
         <v>2</v>
       </c>
       <c r="J33" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>44</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>45</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <v>0</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+      <c r="F35">
+        <v>0</v>
+      </c>
+      <c r="G35">
+        <v>0</v>
+      </c>
+      <c r="H35" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/CODERS scripts/input_files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/electricity_sector/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08131A89-F3AB-48F6-BB95-5DB5CDCD5232}"/>
+  <xr:revisionPtr revIDLastSave="142" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{548260A6-B14F-4DB8-8DDA-3693975CF471}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="-28920" yWindow="2490" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
     <sheet name="ON" sheetId="1" r:id="rId1"/>
@@ -1142,7 +1142,7 @@
         <v>329</v>
       </c>
       <c r="G24">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="H24" t="s">
         <v>32</v>

--- a/input_files/capacity_limits.xlsx
+++ b/input_files/capacity_limits.xlsx
@@ -8,12 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://utoronto-my.sharepoint.com/personal/ian_elder_mail_utoronto_ca/Documents/Documents/TEMOA/electricity_sector/input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="142" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{548260A6-B14F-4DB8-8DDA-3693975CF471}"/>
+  <xr:revisionPtr revIDLastSave="149" documentId="8_{AD9299FD-BE0E-4A8B-BE4E-54B5B8BEA38F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2A7C86A0-032B-4379-B4FC-965CC902B741}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2490" windowWidth="29040" windowHeight="15840" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
+    <workbookView xWindow="-26895" yWindow="4515" windowWidth="21600" windowHeight="11385" firstSheet="5" activeTab="9" xr2:uid="{34B1FE10-2B49-41F7-8CAC-48335CB056E6}"/>
   </bookViews>
   <sheets>
-    <sheet name="ON" sheetId="1" r:id="rId1"/>
+    <sheet name="AB" sheetId="2" r:id="rId1"/>
+    <sheet name="BC" sheetId="3" r:id="rId2"/>
+    <sheet name="MB" sheetId="4" r:id="rId3"/>
+    <sheet name="NB" sheetId="5" r:id="rId4"/>
+    <sheet name="NLLAB" sheetId="6" r:id="rId5"/>
+    <sheet name="NS" sheetId="7" r:id="rId6"/>
+    <sheet name="ON" sheetId="1" r:id="rId7"/>
+    <sheet name="PEI" sheetId="8" r:id="rId8"/>
+    <sheet name="QC" sheetId="9" r:id="rId9"/>
+    <sheet name="SK" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,14 +43,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="45">
   <si>
     <t>tech</t>
   </si>
   <si>
-    <t>max MW per period</t>
-  </si>
-  <si>
     <t>E_SOL_PV-NEW-1</t>
   </si>
   <si>
@@ -112,9 +118,6 @@
   </si>
   <si>
     <t>note</t>
-  </si>
-  <si>
-    <t>Sets the maximum capacity of technologies by period. One sheet per region.</t>
   </si>
   <si>
     <t>dq_est</t>
@@ -532,8 +535,302 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1CC77362-D61B-4F22-8862-ABC495614E3B}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD08374F-5488-4EE8-8E97-6F34735298EC}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63E21237-A4A4-4168-8B4C-00749B38772D}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FCCC26D-DDBF-4180-998D-0597FA53A47D}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBD43877-7723-431F-BDFF-1CBD331E669F}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61673742-8FA0-408F-AFDA-8A9C890F9462}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E07C6694-E75C-452E-8865-BA90EC25C530}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9D36A0F-FD90-42AA-87C7-33795DBA1E16}">
-  <dimension ref="A1:J35"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -542,49 +839,93 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>1</v>
-      </c>
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>1000</v>
+      </c>
+      <c r="C2">
+        <v>1000</v>
+      </c>
+      <c r="D2">
+        <v>1000</v>
+      </c>
+      <c r="E2">
+        <v>1000</v>
+      </c>
+      <c r="F2">
+        <v>1000</v>
+      </c>
+      <c r="G2">
+        <v>1000</v>
+      </c>
+      <c r="H2" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="1"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="B3">
-        <v>2025</v>
+        <v>1000</v>
       </c>
       <c r="C3">
-        <v>2030</v>
+        <v>1000</v>
       </c>
       <c r="D3">
-        <v>2035</v>
+        <v>1000</v>
       </c>
       <c r="E3">
-        <v>2040</v>
+        <v>1000</v>
       </c>
       <c r="F3">
-        <v>2045</v>
+        <v>1000</v>
       </c>
       <c r="G3">
-        <v>2050</v>
+        <v>1000</v>
       </c>
       <c r="H3" t="s">
-        <v>25</v>
-      </c>
-      <c r="I3" t="s">
-        <v>27</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="J3" s="1"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4">
         <v>1000</v>
@@ -605,13 +946,13 @@
         <v>1000</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>1000</v>
@@ -632,13 +973,13 @@
         <v>1000</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B6">
         <v>1000</v>
@@ -659,13 +1000,13 @@
         <v>1000</v>
       </c>
       <c r="H6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7">
         <v>1000</v>
@@ -686,13 +1027,13 @@
         <v>1000</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8">
         <v>1000</v>
@@ -713,13 +1054,13 @@
         <v>1000</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>1000</v>
@@ -740,13 +1081,13 @@
         <v>1000</v>
       </c>
       <c r="H9" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>1000</v>
@@ -767,13 +1108,13 @@
         <v>1000</v>
       </c>
       <c r="H10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11">
         <v>1000</v>
@@ -794,67 +1135,67 @@
         <v>1000</v>
       </c>
       <c r="H11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="B12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="B13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="C13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="D13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="E13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="F13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G13">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J13" s="1"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B14">
         <v>2000</v>
@@ -875,13 +1216,13 @@
         <v>2000</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J14" s="1"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B15">
         <v>2000</v>
@@ -902,13 +1243,13 @@
         <v>2000</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J15" s="1"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B16">
         <v>2000</v>
@@ -929,13 +1270,13 @@
         <v>2000</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J16" s="1"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B17">
         <v>2000</v>
@@ -956,13 +1297,13 @@
         <v>2000</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B18">
         <v>2000</v>
@@ -983,13 +1324,13 @@
         <v>2000</v>
       </c>
       <c r="H18" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J18" s="1"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19">
         <v>2000</v>
@@ -1010,13 +1351,13 @@
         <v>2000</v>
       </c>
       <c r="H19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J19" s="1"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B20">
         <v>2000</v>
@@ -1037,13 +1378,13 @@
         <v>2000</v>
       </c>
       <c r="H20" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J20" s="1"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B21">
         <v>2000</v>
@@ -1064,126 +1405,130 @@
         <v>2000</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J21" s="1"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>2000</v>
+        <v>329</v>
       </c>
       <c r="C22">
-        <v>2000</v>
+        <v>329</v>
       </c>
       <c r="D22">
-        <v>2000</v>
+        <v>329</v>
       </c>
       <c r="E22">
-        <v>2000</v>
+        <v>329</v>
       </c>
       <c r="F22">
-        <v>2000</v>
+        <v>329</v>
       </c>
       <c r="G22">
-        <v>2000</v>
+        <v>329</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
-      </c>
-      <c r="J22" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="C23">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="D23">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="E23">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="F23">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="G23">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
-      </c>
-      <c r="J23" s="1"/>
+        <v>41</v>
+      </c>
+      <c r="I23">
+        <v>2</v>
+      </c>
+      <c r="J23" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="B24">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="D24">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="G24">
-        <v>329</v>
+        <v>0</v>
       </c>
       <c r="H24" t="s">
-        <v>32</v>
-      </c>
-      <c r="I24">
-        <v>1</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B25">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="D25">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="G25">
-        <v>2500</v>
+        <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="I25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J25" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -1209,7 +1554,13 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -1217,31 +1568,31 @@
         <v>36</v>
       </c>
       <c r="B27">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F27">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H27" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J27" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -1249,31 +1600,31 @@
         <v>37</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="H28" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="I28">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J28" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
@@ -1299,13 +1650,13 @@
         <v>500</v>
       </c>
       <c r="H29" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I29">
         <v>2</v>
       </c>
       <c r="J29" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -1331,13 +1682,13 @@
         <v>500</v>
       </c>
       <c r="H30" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I30">
         <v>2</v>
       </c>
       <c r="J30" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -1363,133 +1714,153 @@
         <v>500</v>
       </c>
       <c r="H31" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I31">
         <v>2</v>
       </c>
       <c r="J31" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G32">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>43</v>
       </c>
-      <c r="I32">
-        <v>2</v>
-      </c>
-      <c r="J32" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>42</v>
-      </c>
       <c r="B33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="D33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="G33">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="H33" t="s">
-        <v>43</v>
-      </c>
-      <c r="I33">
-        <v>2</v>
-      </c>
-      <c r="J33" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
         <v>44</v>
-      </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-      <c r="C34">
-        <v>0</v>
-      </c>
-      <c r="D34">
-        <v>0</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-      <c r="F34">
-        <v>0</v>
-      </c>
-      <c r="G34">
-        <v>0</v>
-      </c>
-      <c r="H34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>45</v>
-      </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-      <c r="C35">
-        <v>0</v>
-      </c>
-      <c r="D35">
-        <v>0</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-      <c r="F35">
-        <v>0</v>
-      </c>
-      <c r="G35">
-        <v>0</v>
-      </c>
-      <c r="H35" t="s">
-        <v>46</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B51E1C15-0E3D-4ABE-B298-EE0AF06D1C99}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7E1E526-8DD4-4A1D-89B4-3A66F93DB14F}">
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1">
+        <v>2025</v>
+      </c>
+      <c r="C1">
+        <v>2030</v>
+      </c>
+      <c r="D1">
+        <v>2035</v>
+      </c>
+      <c r="E1">
+        <v>2040</v>
+      </c>
+      <c r="F1">
+        <v>2045</v>
+      </c>
+      <c r="G1">
+        <v>2050</v>
+      </c>
+      <c r="H1" t="s">
+        <v>24</v>
+      </c>
+      <c r="I1" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>